--- a/02_Stakeholder_Analysis/01_Stakeholder_Register/Stakeholder_Register.xlsx
+++ b/02_Stakeholder_Analysis/01_Stakeholder_Register/Stakeholder_Register.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Scale-UP\Digital Loan Application Optimization\Artifact 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39740349-54A6-49F5-814F-90BE5B16BE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBE54D0-F90D-4D3C-B8E8-A130B85EB6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stakeholder Register" sheetId="1" r:id="rId1"/>
-    <sheet name="Next Analysis" sheetId="2" r:id="rId2"/>
+    <sheet name="Power Interest Matrix" sheetId="3" r:id="rId2"/>
+    <sheet name="Next Analysis" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Next Analysis'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Next Analysis'!$A$1:$C$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stakeholder Register'!$A$1:$C$10</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="60">
   <si>
     <t>Stakeholder</t>
   </si>
@@ -181,6 +182,30 @@
   </si>
   <si>
     <t>Identify stakeholder-related risks</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
+    <t>Quadrant</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>🔴 Manage Closely</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>🟢 Keep Informed</t>
+  </si>
+  <si>
+    <t>Low*</t>
   </si>
 </sst>
 </file>
@@ -679,6 +704,162 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE048800-20A8-4372-B2B7-D015B2AE77E1}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.77734375" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/02_Stakeholder_Analysis/01_Stakeholder_Register/Stakeholder_Register.xlsx
+++ b/02_Stakeholder_Analysis/01_Stakeholder_Register/Stakeholder_Register.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Scale-UP\Digital Loan Application Optimization\Artifact 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBE54D0-F90D-4D3C-B8E8-A130B85EB6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F73FF23-6C44-4E49-B5A0-BA2A698B5B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stakeholder Register" sheetId="1" r:id="rId1"/>
     <sheet name="Power Interest Matrix" sheetId="3" r:id="rId2"/>
-    <sheet name="Next Analysis" sheetId="2" r:id="rId3"/>
+    <sheet name="Engagement Strategy" sheetId="4" r:id="rId3"/>
+    <sheet name="Next Analysis" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Next Analysis'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Next Analysis'!$A$1:$C$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stakeholder Register'!$A$1:$C$10</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="112">
   <si>
     <t>Stakeholder</t>
   </si>
@@ -206,6 +207,162 @@
   </si>
   <si>
     <t>Low*</t>
+  </si>
+  <si>
+    <t>Engagement</t>
+  </si>
+  <si>
+    <t>Key information they need</t>
+  </si>
+  <si>
+    <t>Information BA needs</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Sponsor</t>
+  </si>
+  <si>
+    <t>Manage Closely</t>
+  </si>
+  <si>
+    <t>Progress, risks, decisions, business impact</t>
+  </si>
+  <si>
+    <t>Priorities, success criteria, decisions</t>
+  </si>
+  <si>
+    <t>Steering meeting/status report</t>
+  </si>
+  <si>
+    <t>Weekly + major decisions</t>
+  </si>
+  <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>Progress, risks, dependencies</t>
+  </si>
+  <si>
+    <t>Timeline, resources, scope, dependencies</t>
+  </si>
+  <si>
+    <t>Meetings/status updates</t>
+  </si>
+  <si>
+    <t>Weekly + as needed</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>Collaborate/Lead</t>
+  </si>
+  <si>
+    <t>Stakeholder inputs, findings, requirements</t>
+  </si>
+  <si>
+    <t>Information from all relevant stakeholders</t>
+  </si>
+  <si>
+    <t>Interviews, workshops, analysis</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>Product Owner</t>
+  </si>
+  <si>
+    <t>Findings, options, impacts</t>
+  </si>
+  <si>
+    <t>Priorities, business rules, acceptance expectations</t>
+  </si>
+  <si>
+    <t>Workshops/meetings</t>
+  </si>
+  <si>
+    <t>Weekly + decisions</t>
+  </si>
+  <si>
+    <t>Consult/Collaborate</t>
+  </si>
+  <si>
+    <t>Proposed compliance impacts</t>
+  </si>
+  <si>
+    <t>Rules, validation criteria, exceptions</t>
+  </si>
+  <si>
+    <t>Interviews/workshops</t>
+  </si>
+  <si>
+    <t>Discovery + requirement validation</t>
+  </si>
+  <si>
+    <t>Business requirements, scope, process</t>
+  </si>
+  <si>
+    <t>Capabilities, constraints, integrations</t>
+  </si>
+  <si>
+    <t>Workshops/technical discussions</t>
+  </si>
+  <si>
+    <t>Discovery + solution design</t>
+  </si>
+  <si>
+    <t>Keep Informed/Consult</t>
+  </si>
+  <si>
+    <t>Findings, process impacts</t>
+  </si>
+  <si>
+    <t>Operational issues, SLAs, workarounds</t>
+  </si>
+  <si>
+    <t>Discovery + implementation readiness</t>
+  </si>
+  <si>
+    <t>QA/Test</t>
+  </si>
+  <si>
+    <t>Collaborate</t>
+  </si>
+  <si>
+    <t>Requirements, rules, acceptance criteria</t>
+  </si>
+  <si>
+    <t>Testability, edge cases, defects</t>
+  </si>
+  <si>
+    <t>Workshops/test reviews</t>
+  </si>
+  <si>
+    <t>Requirements + testing</t>
+  </si>
+  <si>
+    <t>Customers</t>
+  </si>
+  <si>
+    <t>Consult/Validate</t>
+  </si>
+  <si>
+    <t>Relevant changes and expectations</t>
+  </si>
+  <si>
+    <t>Pain points, usability, behavior</t>
+  </si>
+  <si>
+    <t>Interviews/surveys/usability testing</t>
+  </si>
+  <si>
+    <t>Discovery + validation</t>
   </si>
 </sst>
 </file>
@@ -269,14 +426,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -582,118 +740,118 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.5546875" customWidth="1"/>
-    <col min="2" max="2" width="44.109375" customWidth="1"/>
-    <col min="3" max="3" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.21875" customWidth="1"/>
+    <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -708,149 +866,149 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" customWidth="1"/>
+    <col min="1" max="1" width="24.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.44140625" customWidth="1"/>
     <col min="3" max="3" width="11.21875" customWidth="1"/>
     <col min="4" max="4" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -860,6 +1018,224 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BEB3FDE-7AB7-4343-9315-F8A678DA6700}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23.88671875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="42.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="48.77734375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="35.44140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="37.109375" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -870,112 +1246,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>51</v>
       </c>
     </row>

--- a/02_Stakeholder_Analysis/01_Stakeholder_Register/Stakeholder_Register.xlsx
+++ b/02_Stakeholder_Analysis/01_Stakeholder_Register/Stakeholder_Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Scale-UP\Digital Loan Application Optimization\Artifact 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F73FF23-6C44-4E49-B5A0-BA2A698B5B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8B32AF-10D9-4682-82FD-ABBD041B72AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,11 @@
     <sheet name="Stakeholder Register" sheetId="1" r:id="rId1"/>
     <sheet name="Power Interest Matrix" sheetId="3" r:id="rId2"/>
     <sheet name="Engagement Strategy" sheetId="4" r:id="rId3"/>
-    <sheet name="Next Analysis" sheetId="2" r:id="rId4"/>
+    <sheet name="RACI Matrix" sheetId="5" r:id="rId4"/>
+    <sheet name="Next Analysis" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Next Analysis'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Next Analysis'!$A$1:$C$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stakeholder Register'!$A$1:$C$10</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="140">
   <si>
     <t>Stakeholder</t>
   </si>
@@ -363,13 +364,97 @@
   </si>
   <si>
     <t>Discovery + validation</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Compliance</t>
+  </si>
+  <si>
+    <t>Tech</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Define business problem</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Define scope</t>
+  </si>
+  <si>
+    <t>Stakeholder identification</t>
+  </si>
+  <si>
+    <t>R/A</t>
+  </si>
+  <si>
+    <t>Requirements elicitation</t>
+  </si>
+  <si>
+    <t>AS-IS process analysis</t>
+  </si>
+  <si>
+    <t>Data analysis</t>
+  </si>
+  <si>
+    <t>R/A*</t>
+  </si>
+  <si>
+    <t>Root-cause analysis</t>
+  </si>
+  <si>
+    <t>Define requirements</t>
+  </si>
+  <si>
+    <t>Validate compliance requirements</t>
+  </si>
+  <si>
+    <t>C/R</t>
+  </si>
+  <si>
+    <t>Evaluate solution options</t>
+  </si>
+  <si>
+    <t>Approve recommended solution</t>
+  </si>
+  <si>
+    <t>A*</t>
+  </si>
+  <si>
+    <t>Develop/test solution</t>
+  </si>
+  <si>
+    <t>UAT</t>
+  </si>
+  <si>
+    <t>Go-live</t>
+  </si>
+  <si>
+    <t>Measure business outcome</t>
+  </si>
+  <si>
+    <t>RACI [Responsible, Accountable, Consulted, Informed]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,8 +476,16 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -402,6 +495,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -426,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -435,6 +534,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1236,6 +1341,545 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D110AE-62E9-416E-B27D-01C92B5A0322}">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="34.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" customWidth="1"/>
+    <col min="9" max="9" width="7.21875" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
